--- a/data/output/fpros/fpros_merged_formatted_25.xlsx
+++ b/data/output/fpros/fpros_merged_formatted_25.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F265"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,7 +623,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -698,37 +698,37 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>WR5</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>RB3</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>10</v>
+      <c r="C8" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>DET (8)</t>
+          <t>PHI (9)</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>WR6</t>
+          <t>WR5</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -739,12 +739,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>LAR (8)</t>
+          <t>DET (8)</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -754,30 +754,30 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>RB3</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>WR6</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="7" t="n">
-        <v>3</v>
+      <c r="C10" s="4" t="n">
+        <v>8</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>PHI (9)</t>
+          <t>HOU (6)</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
@@ -791,16 +791,16 @@
         <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>HOU (6)</t>
+          <t>LAR (8)</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -810,53 +810,53 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>WR8</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>RB4</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>11</v>
+      <c r="C12" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Brian Thomas</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>JAC (8)</t>
+          <t>SF (14)</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>WR9</t>
+          <t>WR8</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Brian Thomas</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>ATL (5)</t>
+          <t>JAC (8)</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -866,100 +866,100 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>RB4</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>WR9</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="7" t="n">
-        <v>6</v>
+      <c r="C14" s="4" t="n">
+        <v>13</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>SF (14)</t>
+          <t>ATL (5)</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>WR10</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>RB5</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>Ashton Jeanty (R)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>PHI (9)</t>
+          <t>LV (8)</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>TE1</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>WR10</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Brock Bowers</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>LV (8)</t>
+          <t>PHI (9)</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>RB5</t>
+          <t>RB6</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -978,58 +978,58 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>WR11</t>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>TE1</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="6" t="n">
-        <v>25</v>
+      <c r="C18" s="4" t="n">
+        <v>22</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Brock Bowers</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>LAC (12)</t>
+          <t>LV (8)</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>RB6</t>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>WR11</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C19" s="4" t="n">
-        <v>19</v>
+      <c r="C19" s="6" t="n">
+        <v>23</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>LV (8)</t>
+          <t>LAC (12)</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
@@ -1062,100 +1062,100 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>WR12</t>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>RB7</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C21" s="9" t="n">
-        <v>38</v>
+      <c r="C21" s="7" t="n">
+        <v>16</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>SEA (8)</t>
+          <t>BAL (7)</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>RB7</t>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>WR12</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C22" s="10" t="n">
-        <v>17</v>
+      <c r="C22" s="9" t="n">
+        <v>37</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Derrick Henry</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>BAL (7)</t>
+          <t>SEA (8)</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>WR13</t>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>RB8</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="6" t="n">
-        <v>28</v>
+      <c r="C23" s="4" t="n">
+        <v>25</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>NYJ (9)</t>
+          <t>CIN (10)</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>WR14</t>
+          <t>WR13</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -1202,30 +1202,30 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>WR15</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>RB9</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
         <v>25</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Tyreek Hill</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>MIA (12)</t>
+          <t>TB (9)</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -1258,44 +1258,44 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>RB8</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>WR14</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C28" s="10" t="n">
-        <v>22</v>
+      <c r="C28" s="6" t="n">
+        <v>36</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>CIN (10)</t>
+          <t>NYJ (9)</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>RB9</t>
+          <t>RB10</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C29" s="10" t="n">
-        <v>21</v>
+      <c r="C29" s="7" t="n">
+        <v>18</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
@@ -1314,30 +1314,30 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>RB10</t>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>WR15</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
         <v>29</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Tyreek Hill</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>TB (9)</t>
+          <t>MIA (12)</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
@@ -1350,8 +1350,8 @@
       <c r="B31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C31" s="10" t="n">
-        <v>20</v>
+      <c r="C31" s="7" t="n">
+        <v>19</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -1370,58 +1370,58 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>WR16</t>
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>TE3</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
         <v>31</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>LAR (8)</t>
+          <t>SF (14)</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>TE3</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>WR16</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
         <v>32</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>SF (14)</t>
+          <t>LAR (8)</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
@@ -1434,8 +1434,8 @@
       <c r="B34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="C34" s="6" t="n">
-        <v>40</v>
+      <c r="C34" s="4" t="n">
+        <v>34</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -1490,8 +1490,8 @@
       <c r="B36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="C36" s="6" t="n">
-        <v>44</v>
+      <c r="C36" s="4" t="n">
+        <v>42</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
@@ -1510,72 +1510,72 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>QB4</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>WR18</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="C37" s="4" t="n">
-        <v>34</v>
+      <c r="C37" s="6" t="n">
+        <v>46</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Marvin Harrison</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>PHI (9)</t>
+          <t>ARI (8)</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>WR18</t>
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>QB4</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="C38" s="6" t="n">
-        <v>49</v>
+      <c r="C38" s="4" t="n">
+        <v>33</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Marvin Harrison</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>ARI (8)</t>
+          <t>PHI (9)</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>WR20</t>
+          <t>WR19</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>47</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
@@ -1630,17 +1630,17 @@
       <c r="B41" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="C41" s="4" t="n">
-        <v>45</v>
+      <c r="C41" s="7" t="n">
+        <v>32</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>James Cook</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>NYJ (9)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -1659,7 +1659,7 @@
         <v>42</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -1678,44 +1678,44 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>WR21</t>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>RB16</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="C43" s="6" t="n">
-        <v>54</v>
+      <c r="C43" s="7" t="n">
+        <v>29</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Omarion Hampton (R)</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>PIT (5)</t>
+          <t>LAC (12)</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>WR22</t>
+          <t>WR21</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
         <v>44</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -1736,23 +1736,23 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>RB16</t>
+          <t>RB17</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="C45" s="10" t="n">
-        <v>36</v>
+      <c r="C45" s="4" t="n">
+        <v>53</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>James Cook</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>NYJ (9)</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -1762,86 +1762,86 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>QB5</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>WR22</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="C46" s="4" t="n">
-        <v>57</v>
+      <c r="C46" s="6" t="n">
+        <v>55</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>CIN (10)</t>
+          <t>PIT (5)</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>WR23</t>
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>QB5</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
         <v>47</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>PHI (9)</t>
+          <t>CIN (10)</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>RB17</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>WR23</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="C48" s="7" t="n">
-        <v>29</v>
+      <c r="C48" s="6" t="n">
+        <v>54</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>LAC (12)</t>
+          <t>PHI (9)</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         <v>49</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Tetairoa McMillan (R)</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -1882,8 +1882,8 @@
       <c r="B50" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="C50" s="4" t="n">
-        <v>47</v>
+      <c r="C50" s="7" t="n">
+        <v>43</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
@@ -1910,8 +1910,8 @@
       <c r="B51" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="C51" s="4" t="n">
-        <v>51</v>
+      <c r="C51" s="7" t="n">
+        <v>44</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -1930,44 +1930,44 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>WR25</t>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>RB20</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
         <v>52</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>TreVeyon Henderson (R)</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>BAL (7)</t>
+          <t>NE (14)</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>WR26</t>
+          <t>WR25</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
         <v>53</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
@@ -1988,14 +1988,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>WR27</t>
+          <t>WR26</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="C54" s="7" t="n">
-        <v>32</v>
+      <c r="C54" s="10" t="n">
+        <v>39</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
@@ -2016,23 +2016,23 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>WR28</t>
+          <t>WR27</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
         <v>55</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Calvin Ridley</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>DET (8)</t>
+          <t>TEN (10)</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2044,23 +2044,23 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>WR29</t>
+          <t>WR28</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="C56" s="4" t="n">
-        <v>48</v>
+      <c r="C56" s="7" t="n">
+        <v>38</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Calvin Ridley</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>TEN (10)</t>
+          <t>DAL (10)</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2072,23 +2072,23 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>WR30</t>
+          <t>WR29</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="C57" s="7" t="n">
-        <v>41</v>
+      <c r="C57" s="4" t="n">
+        <v>56</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>DAL (10)</t>
+          <t>BAL (7)</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2100,23 +2100,23 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>WR31</t>
+          <t>WR30</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="C58" s="4" t="n">
-        <v>52</v>
+      <c r="C58" s="6" t="n">
+        <v>64</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>KC (10)</t>
+          <t>DET (8)</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2128,7 +2128,7 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>RB20</t>
+          <t>RB21</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>NE (14)</t>
+          <t>TEN (10)</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -2154,177 +2154,177 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>WR32</t>
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>RB22</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
         <v>60</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>RJ Harvey (R)</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>NO (11)</t>
+          <t>DEN (12)</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>QB6</t>
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>RB23</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
         <v>61</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>KC (10)</t>
+          <t>CHI (5)</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>TE4</t>
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>QB6</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="C62" s="9" t="n">
-        <v>93</v>
+      <c r="C62" s="6" t="n">
+        <v>72</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>T.J. Hockenson</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>KC (10)</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>RB21</t>
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>TE4</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
         <v>63</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>T.J. Hockenson</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>DET (8)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>RB22</t>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>WR31</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="C64" s="9" t="n">
-        <v>79</v>
+      <c r="C64" s="4" t="n">
+        <v>67</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>CHI (5)</t>
+          <t>NO (11)</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>WR33</t>
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>RB24</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="C65" s="7" t="n">
-        <v>42</v>
+      <c r="C65" s="4" t="n">
+        <v>74</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Travis Hunter</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>JAC (8)</t>
+          <t>DET (8)</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>RB23</t>
+          <t>RB25</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Isiah Pacheco</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>TEN (10)</t>
+          <t>KC (10)</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -2350,254 +2350,254 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>WR34</t>
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>RB26</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
         <v>67</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Jerry Jeudy</t>
+          <t>Aaron Jones</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>CLE (9)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>RB24</t>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>WR32</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="C68" s="4" t="n">
-        <v>78</v>
+      <c r="C68" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Aaron Jones</t>
+          <t>Travis Hunter (R)</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>JAC (8)</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>QB7</t>
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>TE5</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="C69" s="9" t="n">
-        <v>106</v>
+      <c r="C69" s="4" t="n">
+        <v>79</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Baker Mayfield</t>
+          <t>Sam LaPorta</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>TB (9)</t>
+          <t>DET (8)</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>RB25</t>
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>QB7</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C70" s="4" t="n">
-        <v>72</v>
+      <c r="C70" s="9" t="n">
+        <v>106</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Isiah Pacheco</t>
+          <t>Baker Mayfield</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>KC (10)</t>
+          <t>TB (9)</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>RB26</t>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>WR33</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
         <v>71</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>RJ Harvey</t>
+          <t>Rashee Rice (?)</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>DEN (12)</t>
+          <t>KC (10)</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>TE5</t>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>WR34</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
         <v>72</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Sam LaPorta</t>
+          <t>Jerry Jeudy</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>DET (8)</t>
+          <t>CLE (9)</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>TE6</t>
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>QB8</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="C73" s="4" t="n">
-        <v>91</v>
+      <c r="C73" s="9" t="n">
+        <v>86</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Travis Kelce</t>
+          <t>Bo Nix</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>KC (10)</t>
+          <t>DEN (12)</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>QB8</t>
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>WR35</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
         <v>74</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Bo Nix</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>DEN (12)</t>
+          <t>CHI (5)</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>WR35</t>
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>TE6</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
         <v>75</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>Travis Kelce</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>NE (14)</t>
+          <t>KC (10)</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
@@ -2610,17 +2610,17 @@
       <c r="B76" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C76" s="7" t="n">
-        <v>59</v>
+      <c r="C76" s="4" t="n">
+        <v>71</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Jakobi Meyers</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>LV (8)</t>
+          <t>NE (14)</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -2638,17 +2638,17 @@
       <c r="B77" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="C77" s="10" t="n">
-        <v>65</v>
+      <c r="C77" s="7" t="n">
+        <v>49</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Emeka Egbuka (R)</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>CHI (5)</t>
+          <t>TB (9)</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -2658,109 +2658,109 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>QB9</t>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>WR38</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
         <v>78</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>Ricky Pearsall</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>ARI (8)</t>
+          <t>SF (14)</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t>TE7</t>
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>QB9</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="C79" s="9" t="n">
-        <v>127</v>
+      <c r="C79" s="4" t="n">
+        <v>87</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>David Njoku</t>
+          <t>Kyler Murray</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>CLE (9)</t>
+          <t>ARI (8)</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>TE8</t>
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>RB27</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="C80" s="9" t="n">
-        <v>119</v>
+      <c r="C80" s="4" t="n">
+        <v>110</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Evan Engram</t>
+          <t>Tyrone Tracy</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>DEN (12)</t>
+          <t>NYG (14)</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>RB27</t>
+          <t>RB28</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="C81" s="9" t="n">
+      <c r="C81" s="4" t="n">
         <v>109</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Tyrone Tracy</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>NYG (14)</t>
+          <t>PIT (5)</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -2770,137 +2770,137 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t>QB10</t>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>WR39</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="C82" s="9" t="n">
-        <v>114</v>
+      <c r="C82" s="4" t="n">
+        <v>69</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jakobi Meyers</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>DAL (10)</t>
+          <t>LV (8)</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>RB28</t>
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>QB10</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="C83" s="4" t="n">
-        <v>94</v>
+      <c r="C83" s="9" t="n">
+        <v>107</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>PIT (5)</t>
+          <t>DAL (10)</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>RB29</t>
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>TE7</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="C84" s="4" t="n">
-        <v>86</v>
+      <c r="C84" s="9" t="n">
+        <v>122</v>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Kaleb Johnson</t>
+          <t>David Njoku</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>PIT (5)</t>
+          <t>CLE (9)</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>WR38</t>
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>TE8</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="C85" s="9" t="n">
-        <v>98</v>
+      <c r="C85" s="4" t="n">
+        <v>105</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Chris Godwin</t>
+          <t>Evan Engram</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>TB (9)</t>
+          <t>DEN (12)</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>RB30</t>
+          <t>RB29</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
         <v>86</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Brian Robinson</t>
+          <t>Kaleb Johnson (R)</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>WAS (12)</t>
+          <t>PIT (5)</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -2910,137 +2910,137 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>WR39</t>
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>TE9</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
         <v>87</v>
       </c>
       <c r="C87" s="4" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Ricky Pearsall</t>
+          <t>Mark Andrews</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>SF (14)</t>
+          <t>BAL (7)</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>WR40</t>
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>QB11</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
         <v>88</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Khalil Shakir</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>SF (14)</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t>TE9</t>
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>RB30</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
         <v>89</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Mark Andrews</t>
+          <t>Travis Etienne</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>BAL (7)</t>
+          <t>JAC (8)</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>WR41</t>
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>QB12</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="C90" s="7" t="n">
-        <v>62</v>
+      <c r="C90" s="9" t="n">
+        <v>112</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Jauan Jennings</t>
+          <t>Justin Fields</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>SF (14)</t>
+          <t>NYJ (9)</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>WR42</t>
+          <t>WR40</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="C91" s="10" t="n">
-        <v>76</v>
+      <c r="C91" s="6" t="n">
+        <v>103</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Jordan Addison</t>
+          <t>Khalil Shakir</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -3050,30 +3050,30 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="11" t="inlineStr">
-        <is>
-          <t>QB11</t>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>WR41</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
         <v>92</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Justin Fields</t>
+          <t>Jordan Addison (?)</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>NYJ (9)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
@@ -3087,16 +3087,16 @@
         <v>93</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Joe Mixon</t>
+          <t>Zach Charbonnet</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>HOU (6)</t>
+          <t>SEA (8)</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -3106,132 +3106,132 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t>QB12</t>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>WR42</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
         <v>94</v>
       </c>
       <c r="C94" s="10" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Deebo Samuel</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>SF (14)</t>
+          <t>WAS (12)</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>RB32</t>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>WR43</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="C95" s="4" t="n">
-        <v>85</v>
+      <c r="C95" s="7" t="n">
+        <v>62</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Travis Etienne</t>
+          <t>Jauan Jennings</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>JAC (8)</t>
+          <t>SF (14)</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="11" t="inlineStr">
-        <is>
-          <t>QB13</t>
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>WR44</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
         <v>96</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Josh Downs</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>LAC (12)</t>
+          <t>IND (11)</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>WR43</t>
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>QB13</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="C97" s="7" t="n">
-        <v>70</v>
+      <c r="C97" s="9" t="n">
+        <v>111</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Deebo Samuel</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>WAS (12)</t>
+          <t>LAC (12)</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>WR44</t>
+          <t>WR45</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="C98" s="10" t="n">
-        <v>81</v>
+      <c r="C98" s="4" t="n">
+        <v>93</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Josh Downs</t>
+          <t>Michael Pittman</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -3255,16 +3255,16 @@
         <v>99</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Jared Goff</t>
+          <t>Caleb Williams</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>DET (8)</t>
+          <t>CHI (5)</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -3274,137 +3274,137 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>WR45</t>
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>RB32</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="C100" s="10" t="n">
-        <v>82</v>
+      <c r="C100" s="4" t="n">
+        <v>129</v>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Michael Pittman</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>IND (11)</t>
+          <t>DAL (10)</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>WR46</t>
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>QB15</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="C101" s="7" t="n">
-        <v>69</v>
+      <c r="C101" s="4" t="n">
+        <v>113</v>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Drake Maye</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>TB (9)</t>
+          <t>NE (14)</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t>QB15</t>
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>RB33</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
         <v>102</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>NE (14)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="11" t="inlineStr">
-        <is>
-          <t>QB16</t>
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>TE10</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="C103" s="4" t="n">
-        <v>115</v>
+      <c r="C103" s="7" t="n">
+        <v>92</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Caleb Williams</t>
+          <t>Tyler Warren (R)</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>CHI (5)</t>
+          <t>IND (11)</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>WR47</t>
+          <t>WR46</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
         <v>104</v>
       </c>
-      <c r="C104" s="4" t="n">
-        <v>105</v>
+      <c r="C104" s="7" t="n">
+        <v>57</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Cooper Kupp</t>
+          <t>Matthew Golden (R)</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>SEA (8)</t>
+          <t>GB (5)</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -3414,44 +3414,44 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>WR48</t>
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>QB16</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
         <v>105</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Jared Goff</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>GB (5)</t>
+          <t>DET (8)</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>TE10</t>
+          <t>TE11</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="C106" s="10" t="n">
-        <v>100</v>
+      <c r="C106" s="7" t="n">
+        <v>90</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
@@ -3470,142 +3470,142 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>RB33</t>
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>WR47</t>
         </is>
       </c>
       <c r="B107" s="3" t="n">
         <v>107</v>
       </c>
-      <c r="C107" s="9" t="n">
-        <v>155</v>
+      <c r="C107" s="4" t="n">
+        <v>98</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Cooper Kupp</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>DAL (10)</t>
+          <t>SEA (8)</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t>TE11</t>
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>WR48</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="C108" s="4" t="n">
-        <v>126</v>
+      <c r="C108" s="9" t="n">
+        <v>125</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Jake Ferguson</t>
+          <t>Chris Godwin (?)</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>DAL (10)</t>
+          <t>TB (9)</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t>QB17</t>
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>TE12</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
         <v>109</v>
       </c>
       <c r="C109" s="4" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Jordan Love</t>
+          <t>Jake Ferguson</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>GB (5)</t>
+          <t>DAL (10)</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>RB34</t>
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>QB17</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="C110" s="10" t="n">
-        <v>88</v>
+      <c r="C110" s="4" t="n">
+        <v>121</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Jordan Love</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>GB (5)</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>RB35</t>
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>WR49</t>
         </is>
       </c>
       <c r="B111" s="3" t="n">
         <v>111</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Zach Charbonnet</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>SEA (8)</t>
+          <t>GB (5)</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
@@ -3618,8 +3618,8 @@
       <c r="B112" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="C112" s="4" t="n">
-        <v>129</v>
+      <c r="C112" s="9" t="n">
+        <v>134</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
@@ -3640,23 +3640,23 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>RB36</t>
+          <t>RB34</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
         <v>113</v>
       </c>
       <c r="C113" s="4" t="n">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Jacory Croskey-Merritt (R)</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>NE (14)</t>
+          <t>WAS (12)</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -3666,142 +3666,142 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="inlineStr">
-        <is>
-          <t>TE12</t>
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>RB35</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
         <v>114</v>
       </c>
       <c r="C114" s="7" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Tyler Warren</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>IND (11)</t>
+          <t>DEN (12)</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="11" t="inlineStr">
-        <is>
-          <t>QB19</t>
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>RB36</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
         <v>115</v>
       </c>
       <c r="C115" s="4" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Austin Ekeler</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>HOU (6)</t>
+          <t>WAS (12)</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>WR49</t>
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>QB19</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="C116" s="7" t="n">
-        <v>53</v>
+      <c r="C116" s="9" t="n">
+        <v>133</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>GB (5)</t>
+          <t>HOU (6)</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>RB37</t>
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>QB20</t>
         </is>
       </c>
       <c r="B117" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="C117" s="10" t="n">
-        <v>95</v>
+      <c r="C117" s="9" t="n">
+        <v>150</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>DEN (12)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>WR50</t>
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>RB37</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="C118" s="7" t="n">
-        <v>83</v>
+      <c r="C118" s="4" t="n">
+        <v>116</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Darnell Mooney</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>ATL (5)</t>
+          <t>NE (14)</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
@@ -3814,8 +3814,8 @@
       <c r="B119" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="C119" s="4" t="n">
-        <v>120</v>
+      <c r="C119" s="10" t="n">
+        <v>115</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
@@ -3834,76 +3834,76 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t>QB20</t>
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>WR50</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="C120" s="4" t="n">
-        <v>132</v>
+      <c r="C120" s="7" t="n">
+        <v>82</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>ATL (5)</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="8" t="inlineStr">
-        <is>
-          <t>TE14</t>
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>RB38</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
         <v>121</v>
       </c>
       <c r="C121" s="4" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Dallas Goedert</t>
+          <t>Tank Bigsby</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>PHI (9)</t>
+          <t>JAC (8)</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>RB38</t>
+          <t>RB39</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="C122" s="4" t="n">
-        <v>108</v>
+      <c r="C122" s="7" t="n">
+        <v>100</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Cam Skattebo (R)</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
@@ -3927,16 +3927,16 @@
         <v>123</v>
       </c>
       <c r="C123" s="4" t="n">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Brandon Aiyuk</t>
+          <t>Keon Coleman</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>SF (14)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -3946,81 +3946,81 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>RB39</t>
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>TE14</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="C124" s="9" t="n">
-        <v>164</v>
+      <c r="C124" s="4" t="n">
+        <v>135</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>Dallas Goedert</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>TB (9)</t>
+          <t>PHI (9)</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>WR52</t>
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>TE15</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="C125" s="10" t="n">
-        <v>103</v>
+      <c r="C125" s="7" t="n">
+        <v>91</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Rashid Shaheed</t>
+          <t>Colston Loveland (R)</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>NO (11)</t>
+          <t>CHI (5)</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>WR53</t>
+          <t>WR52</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
         <v>126</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Keon Coleman</t>
+          <t>Christian Kirk</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>HOU (6)</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -4030,53 +4030,53 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>RB40</t>
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>WR53</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="C127" s="9" t="n">
-        <v>153</v>
+      <c r="C127" s="7" t="n">
+        <v>83</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Tank Bigsby</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>JAC (8)</t>
+          <t>NO (11)</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>RB41</t>
+          <t>RB40</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="C128" s="9" t="n">
-        <v>150</v>
+      <c r="C128" s="4" t="n">
+        <v>166</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Tyjae Spears</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>TEN (10)</t>
+          <t>TB (9)</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -4086,30 +4086,30 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>RB42</t>
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>QB21</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
         <v>129</v>
       </c>
       <c r="C129" s="9" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Najee Harris</t>
+          <t>Tua Tagovailoa</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>LAC (12)</t>
+          <t>MIA (12)</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
@@ -4123,16 +4123,16 @@
         <v>130</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Christian Kirk</t>
+          <t>Brandon Aiyuk (?)</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>HOU (6)</t>
+          <t>SF (14)</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -4142,137 +4142,137 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="11" t="inlineStr">
-        <is>
-          <t>QB21</t>
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>RB41</t>
         </is>
       </c>
       <c r="B131" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="C131" s="4" t="n">
-        <v>146</v>
+      <c r="C131" s="10" t="n">
+        <v>126</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa</t>
+          <t>Braelon Allen</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>MIA (12)</t>
+          <t>NYJ (9)</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="8" t="inlineStr">
-        <is>
-          <t>TE15</t>
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>QB22</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="C132" s="7" t="n">
-        <v>101</v>
+      <c r="C132" s="4" t="n">
+        <v>140</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>Bryce Young</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>CHI (5)</t>
+          <t>CAR (14)</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="11" t="inlineStr">
-        <is>
-          <t>QB22</t>
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>RB42</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
         <v>133</v>
       </c>
       <c r="C133" s="4" t="n">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Najee Harris</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>CAR (14)</t>
+          <t>LAC (12)</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>RB43</t>
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>QB23</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
         <v>134</v>
       </c>
       <c r="C134" s="9" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Michael Penix</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>CLE (9)</t>
+          <t>ATL (5)</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>RB44</t>
+          <t>RB43</t>
         </is>
       </c>
       <c r="B135" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="C135" s="9" t="n">
-        <v>163</v>
+      <c r="C135" s="7" t="n">
+        <v>117</v>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Austin Ekeler</t>
+          <t>Joe Mixon</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>WAS (12)</t>
+          <t>HOU (6)</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -4282,81 +4282,81 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>WR55</t>
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>RB44</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
         <v>136</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Cedric Tillman</t>
+          <t>Tyjae Spears</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
+          <t>TEN (10)</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>RB45</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="C137" s="4" t="n">
+        <v>163</v>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins (R)</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
           <t>CLE (9)</t>
         </is>
       </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t>QB23</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="n">
-        <v>138</v>
-      </c>
-      <c r="C137" s="4" t="n">
-        <v>147</v>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>Michael Penix</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>ATL (5)</t>
-        </is>
-      </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>RB45</t>
+          <t>RB46</t>
         </is>
       </c>
       <c r="B138" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C138" s="10" t="n">
-        <v>118</v>
+      <c r="C138" s="4" t="n">
+        <v>153</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Ray Davis</t>
+          <t>Trey Benson</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>ARI (8)</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -4366,165 +4366,165 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="8" t="inlineStr">
-        <is>
-          <t>TE16</t>
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>WR56</t>
         </is>
       </c>
       <c r="B139" s="3" t="n">
         <v>140</v>
       </c>
       <c r="C139" s="4" t="n">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Hunter Henry</t>
+          <t>Cedric Tillman</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>NE (14)</t>
+          <t>CLE (9)</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>WR57</t>
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t>TE16</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="C140" s="7" t="n">
-        <v>112</v>
+      <c r="C140" s="4" t="n">
+        <v>144</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Rashod Bateman</t>
+          <t>Kyle Pitts (?)</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>BAL (7)</t>
+          <t>ATL (5)</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="11" t="inlineStr">
-        <is>
-          <t>QB24</t>
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>TE17</t>
         </is>
       </c>
       <c r="B141" s="3" t="n">
         <v>142</v>
       </c>
       <c r="C141" s="4" t="n">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Matthew Stafford</t>
+          <t>Hunter Henry</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>LAR (8)</t>
+          <t>NE (14)</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t>RB46</t>
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>WR57</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
         <v>143</v>
       </c>
       <c r="C142" s="4" t="n">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Jerome Ford</t>
+          <t>Rashod Bateman</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>CLE (9)</t>
+          <t>BAL (7)</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>RB47</t>
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>WR58</t>
         </is>
       </c>
       <c r="B143" s="3" t="n">
         <v>144</v>
       </c>
       <c r="C143" s="4" t="n">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Braelon Allen</t>
+          <t>Marvin Mims</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>NYJ (9)</t>
+          <t>DEN (12)</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>RB48</t>
+          <t>RB47</t>
         </is>
       </c>
       <c r="B144" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="C144" s="4" t="n">
-        <v>151</v>
+      <c r="C144" s="10" t="n">
+        <v>138</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Trey Benson</t>
+          <t>Brian Robinson</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>ARI (8)</t>
+          <t>SF (14)</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -4536,23 +4536,23 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>RB49</t>
+          <t>RB48</t>
         </is>
       </c>
       <c r="B145" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="C145" s="9" t="n">
-        <v>188</v>
+      <c r="C145" s="7" t="n">
+        <v>127</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Jaydon Blue</t>
+          <t>Ray Davis</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>DAL (10)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -4562,53 +4562,53 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>WR58</t>
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>QB24</t>
         </is>
       </c>
       <c r="B146" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="C146" s="10" t="n">
-        <v>124</v>
+      <c r="C146" s="9" t="n">
+        <v>178</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Marvin Mims</t>
+          <t>Matthew Stafford</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>DEN (12)</t>
+          <t>LAR (8)</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>RB50</t>
+          <t>RB49</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
         <v>148</v>
       </c>
       <c r="C147" s="4" t="n">
-        <v>138</v>
+        <v>196</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Jaydon Blue (R)</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>ATL (5)</t>
+          <t>DAL (10)</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -4618,76 +4618,76 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>WR59</t>
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>QB25</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
         <v>149</v>
       </c>
       <c r="C148" s="4" t="n">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Romeo Doubs</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>GB (5)</t>
+          <t>LV (8)</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="8" t="inlineStr">
-        <is>
-          <t>TE17</t>
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>RB50</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
         <v>150</v>
       </c>
       <c r="C149" s="4" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Jonnu Smith</t>
+          <t>Jerome Ford</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>PIT (5)</t>
+          <t>CLE (9)</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>WR60</t>
+          <t>WR59</t>
         </is>
       </c>
       <c r="B150" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="C150" s="7" t="n">
-        <v>104</v>
+      <c r="C150" s="4" t="n">
+        <v>124</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Jayden Higgins</t>
+          <t>Jayden Higgins (R)</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -4702,48 +4702,48 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="11" t="inlineStr">
-        <is>
-          <t>QB25</t>
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>RB51</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="C151" s="4" t="n">
-        <v>154</v>
+      <c r="C151" s="7" t="n">
+        <v>131</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>Bhayshul Tuten (R)</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>LV (8)</t>
+          <t>JAC (8)</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="8" t="inlineStr">
-        <is>
-          <t>TE18</t>
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>RB52</t>
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C152" s="7" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Kyle Pitts</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
@@ -4753,30 +4753,30 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>RB51</t>
+          <t>RB53</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>155</v>
-      </c>
-      <c r="C153" s="4" t="n">
-        <v>152</v>
+        <v>154</v>
+      </c>
+      <c r="C153" s="7" t="n">
+        <v>101</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>Dylan Sampson (R)</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>CAR (14)</t>
+          <t>CLE (9)</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -4788,14 +4788,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>WR62</t>
+          <t>WR60</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C154" s="6" t="n">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
@@ -4816,14 +4816,14 @@
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>TE19</t>
+          <t>TE18</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
@@ -4844,23 +4844,23 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>RB52</t>
+          <t>RB54</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="C156" s="4" t="n">
         <v>158</v>
       </c>
-      <c r="C156" s="4" t="n">
-        <v>137</v>
-      </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Isaac Guerendo</t>
+          <t>Nick Chubb</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>SF (14)</t>
+          <t>HOU (6)</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -4872,23 +4872,23 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>WR63</t>
+          <t>WR61</t>
         </is>
       </c>
       <c r="B157" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="C157" s="6" t="n">
-        <v>221</v>
+      <c r="C157" s="7" t="n">
+        <v>104</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Adam Thielen</t>
+          <t>Keenan Allen</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>CAR (14)</t>
+          <t>LAC (12)</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -4898,53 +4898,53 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>WR64</t>
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t>TE19</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
         <v>160</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Demario Douglas</t>
+          <t>Jonnu Smith</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>NE (14)</t>
+          <t>PIT (5)</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>WR65</t>
+          <t>WR62</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Kyle Williams</t>
+          <t>Romeo Doubs</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>NE (14)</t>
+          <t>GB (5)</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -4954,198 +4954,198 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="11" t="inlineStr">
-        <is>
-          <t>QB26</t>
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>WR64</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
         <v>163</v>
       </c>
       <c r="C160" s="4" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Cameron Ward</t>
+          <t>Demario Douglas</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>TEN (10)</t>
+          <t>NE (14)</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>RB53</t>
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>WR65</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="C161" s="4" t="n">
-        <v>142</v>
+      <c r="C161" s="6" t="n">
+        <v>202</v>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten</t>
+          <t>Adam Thielen</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>JAC (8)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t>RB54</t>
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t>QB26</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="C162" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Cam Ward (R)</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>TEN (10)</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>QB27</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="C162" s="10" t="n">
-        <v>136</v>
-      </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>Dylan Sampson</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="inlineStr">
-        <is>
-          <t>CLE (9)</t>
-        </is>
-      </c>
-      <c r="F162" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>WR67</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="C163" s="7" t="n">
-        <v>99</v>
+      <c r="C163" s="4" t="n">
+        <v>161</v>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Keenan Allen</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>LAC (12)</t>
+          <t>SEA (8)</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="inlineStr">
-        <is>
-          <t>RB55</t>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>WR66</t>
         </is>
       </c>
       <c r="B164" s="3" t="n">
         <v>168</v>
       </c>
       <c r="C164" s="4" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Jaylen Wright</t>
+          <t>Kyle Williams (R)</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>MIA (12)</t>
+          <t>NE (14)</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="11" t="inlineStr">
-        <is>
-          <t>QB27</t>
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>RB55</t>
         </is>
       </c>
       <c r="B165" s="3" t="n">
         <v>169</v>
       </c>
       <c r="C165" s="4" t="n">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>SEA (8)</t>
+          <t>CAR (14)</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="5" t="inlineStr">
-        <is>
-          <t>RB56</t>
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>WR67</t>
         </is>
       </c>
       <c r="B166" s="3" t="n">
         <v>170</v>
       </c>
       <c r="C166" s="6" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Nick Chubb</t>
+          <t>Tre' Harris (R)</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>HOU (6)</t>
+          <t>LAC (12)</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
         <v>171</v>
       </c>
       <c r="C167" s="4" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
@@ -5184,19 +5184,19 @@
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Joshua Palmer</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>LAC (12)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C169" s="4" t="n">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
@@ -5240,19 +5240,19 @@
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="C170" s="10" t="n">
-        <v>144</v>
+        <v>177</v>
+      </c>
+      <c r="C170" s="4" t="n">
+        <v>184</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Joshua Palmer</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>LAC (12)</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -5268,243 +5268,243 @@
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C171" s="4" t="n">
+        <v>183</v>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Jalen Coker</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>CAR (14)</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="8" t="inlineStr">
+        <is>
+          <t>TE21</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="C172" s="10" t="n">
+        <v>145</v>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Chig Okonkwo</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>TEN (10)</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>RB56</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="n">
+        <v>184</v>
+      </c>
+      <c r="C173" s="4" t="n">
+        <v>193</v>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>Isaac Guerendo</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>SF (14)</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>RB57</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="C174" s="4" t="n">
+        <v>186</v>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>LAR (8)</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>RB58</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="n">
+        <v>188</v>
+      </c>
+      <c r="C175" s="4" t="n">
+        <v>187</v>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>Ollie Gordon (R)</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>MIA (12)</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>RB59</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="C176" s="6" t="n">
+        <v>223</v>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>Woody Marks (R)</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>HOU (6)</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>RB60</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="C177" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>Roschon Johnson</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>CHI (5)</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>WR72</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>Jalen McMillan</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>TB (9)</t>
-        </is>
-      </c>
-      <c r="F171" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="5" t="inlineStr">
-        <is>
-          <t>RB57</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="n">
-        <v>179</v>
-      </c>
-      <c r="C172" s="4" t="n">
-        <v>166</v>
-      </c>
-      <c r="D172" s="3" t="inlineStr">
-        <is>
-          <t>Roschon Johnson</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="inlineStr">
-        <is>
-          <t>CHI (5)</t>
-        </is>
-      </c>
-      <c r="F172" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>WR72</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="n">
-        <v>181</v>
-      </c>
-      <c r="C173" s="4" t="n">
-        <v>182</v>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
+      <c r="C178" s="4" t="n">
+        <v>197</v>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t>DeAndre Hopkins</t>
         </is>
       </c>
-      <c r="E173" s="3" t="inlineStr">
+      <c r="E178" s="3" t="inlineStr">
         <is>
           <t>BAL (7)</t>
         </is>
       </c>
-      <c r="F173" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="8" t="inlineStr">
-        <is>
-          <t>TE21</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="n">
-        <v>183</v>
-      </c>
-      <c r="C174" s="4" t="n">
-        <v>159</v>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>Chig Okonkwo</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="inlineStr">
-        <is>
-          <t>TEN (10)</t>
-        </is>
-      </c>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="8" t="inlineStr">
-        <is>
-          <t>TE22</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="n">
-        <v>184</v>
-      </c>
-      <c r="C175" s="4" t="n">
-        <v>208</v>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>Mike Gesicki</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="inlineStr">
-        <is>
-          <t>CIN (10)</t>
-        </is>
-      </c>
-      <c r="F175" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="11" t="inlineStr">
-        <is>
-          <t>QB28</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="n">
-        <v>186</v>
-      </c>
-      <c r="C176" s="4" t="n">
-        <v>194</v>
-      </c>
-      <c r="D176" s="3" t="inlineStr">
-        <is>
-          <t>Aaron Rodgers</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="inlineStr">
-        <is>
-          <t>PIT (5)</t>
-        </is>
-      </c>
-      <c r="F176" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="8" t="inlineStr">
-        <is>
-          <t>TE23</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="C177" s="6" t="n">
-        <v>238</v>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>Pat Freiermuth</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>PIT (5)</t>
-        </is>
-      </c>
-      <c r="F177" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="5" t="inlineStr">
-        <is>
-          <t>RB58</t>
-        </is>
-      </c>
-      <c r="B178" s="3" t="n">
-        <v>188</v>
-      </c>
-      <c r="C178" s="4" t="n">
-        <v>190</v>
-      </c>
-      <c r="D178" s="3" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>LAR (8)</t>
-        </is>
-      </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>RB59</t>
+          <t>RB61</t>
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C179" s="4" t="n">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Jaylen Wright</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>GB (5)</t>
+          <t>MIA (12)</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -5514,114 +5514,114 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>WR73</t>
+      <c r="A180" s="8" t="inlineStr">
+        <is>
+          <t>TE22</t>
         </is>
       </c>
       <c r="B180" s="3" t="n">
         <v>195</v>
       </c>
       <c r="C180" s="4" t="n">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Jalen Coker</t>
+          <t>Cade Otton</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>CAR (14)</t>
+          <t>TB (9)</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>WR74</t>
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>QB28</t>
         </is>
       </c>
       <c r="B181" s="3" t="n">
         <v>196</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>Alec Pierce</t>
+          <t>Aaron Rodgers</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>IND (11)</t>
+          <t>PIT (5)</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="8" t="inlineStr">
         <is>
+          <t>TE23</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="C182" s="4" t="n">
+        <v>209</v>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>Mike Gesicki</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>CIN (10)</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="8" t="inlineStr">
+        <is>
           <t>TE24</t>
         </is>
       </c>
-      <c r="B182" s="3" t="n">
-        <v>198</v>
-      </c>
-      <c r="C182" s="10" t="n">
-        <v>167</v>
-      </c>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="inlineStr">
-        <is>
-          <t>BAL (7)</t>
-        </is>
-      </c>
-      <c r="F182" s="3" t="inlineStr">
+      <c r="B183" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="C183" s="6" t="n">
+        <v>255</v>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>Pat Freiermuth</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>PIT (5)</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>WR75</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="n">
-        <v>203</v>
-      </c>
-      <c r="C183" s="4" t="n">
-        <v>174</v>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>ARI (8)</t>
-        </is>
-      </c>
-      <c r="F183" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
@@ -5632,14 +5632,14 @@
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>204</v>
-      </c>
-      <c r="C184" s="4" t="n">
-        <v>198</v>
+        <v>206</v>
+      </c>
+      <c r="C184" s="10" t="n">
+        <v>162</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Mason Taylor</t>
+          <t>Mason Taylor (R)</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
@@ -5660,19 +5660,19 @@
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>205</v>
-      </c>
-      <c r="C185" s="4" t="n">
-        <v>201</v>
+        <v>207</v>
+      </c>
+      <c r="C185" s="10" t="n">
+        <v>172</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Cade Otton</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>TB (9)</t>
+          <t>BAL (7)</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -5684,23 +5684,23 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>WR76</t>
+          <t>WR73</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C186" s="4" t="n">
-        <v>218</v>
+        <v>182</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Jack Bech</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>LV (8)</t>
+          <t>ARI (8)</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -5710,20 +5710,20 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="11" t="inlineStr">
-        <is>
-          <t>QB29</t>
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>WR74</t>
         </is>
       </c>
       <c r="B187" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="C187" s="10" t="n">
-        <v>175</v>
+      <c r="C187" s="4" t="n">
+        <v>201</v>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Anthony Richardson</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
@@ -5733,30 +5733,30 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>RB60</t>
+          <t>RB62</t>
         </is>
       </c>
       <c r="B188" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="C188" s="4" t="n">
-        <v>204</v>
+      <c r="C188" s="10" t="n">
+        <v>139</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Justice Hill</t>
+          <t>Will Shipley</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>BAL (7)</t>
+          <t>PHI (9)</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
@@ -5768,23 +5768,23 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>WR77</t>
+          <t>WR75</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>213</v>
-      </c>
-      <c r="C189" s="10" t="n">
-        <v>140</v>
+        <v>212</v>
+      </c>
+      <c r="C189" s="4" t="n">
+        <v>240</v>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Darius Slayton</t>
+          <t>Jack Bech (R)</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>NYG (14)</t>
+          <t>LV (8)</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -5796,14 +5796,14 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>WR78</t>
+          <t>WR76</t>
         </is>
       </c>
       <c r="B190" s="3" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C190" s="4" t="n">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
@@ -5824,23 +5824,23 @@
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>RB61</t>
+          <t>RB63</t>
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C191" s="4" t="n">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Kareem Hunt</t>
+          <t>Justice Hill</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>KC (10)</t>
+          <t>BAL (7)</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
@@ -5852,23 +5852,23 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>WR79</t>
+          <t>WR77</t>
         </is>
       </c>
       <c r="B192" s="3" t="n">
         <v>219</v>
       </c>
       <c r="C192" s="4" t="n">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks</t>
+          <t>Pat Bryant (R)</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>GB (5)</t>
+          <t>DEN (12)</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
@@ -5878,193 +5878,193 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="5" t="inlineStr">
-        <is>
-          <t>RB62</t>
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>WR78</t>
         </is>
       </c>
       <c r="B193" s="3" t="n">
         <v>220</v>
       </c>
       <c r="C193" s="10" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Will Shipley</t>
+          <t>Darius Slayton</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>PHI (9)</t>
+          <t>NYG (14)</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="5" t="inlineStr">
-        <is>
-          <t>RB63</t>
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>WR79</t>
         </is>
       </c>
       <c r="B194" s="3" t="n">
         <v>221</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Kendre Miller</t>
+          <t>Elic Ayomanor (R)</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>NO (11)</t>
+          <t>TEN (10)</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="8" t="inlineStr">
-        <is>
-          <t>TE27</t>
+      <c r="A195" s="11" t="inlineStr">
+        <is>
+          <t>QB29</t>
         </is>
       </c>
       <c r="B195" s="3" t="n">
         <v>222</v>
       </c>
-      <c r="C195" s="4" t="n">
-        <v>202</v>
+      <c r="C195" s="10" t="n">
+        <v>179</v>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>Dalton Schultz</t>
+          <t>Daniel Jones</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>HOU (6)</t>
+          <t>IND (11)</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>WR80</t>
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>RB64</t>
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="C196" s="4" t="n">
-        <v>211</v>
+        <v>224</v>
+      </c>
+      <c r="C196" s="10" t="n">
+        <v>169</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Andrei Iosivas</t>
+          <t>DJ Giddens (R)</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>CIN (10)</t>
+          <t>IND (11)</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>WR81</t>
+          <t>WR80</t>
         </is>
       </c>
       <c r="B197" s="3" t="n">
+        <v>225</v>
+      </c>
+      <c r="C197" s="4" t="n">
+        <v>217</v>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>Andrei Iosivas</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>CIN (10)</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t>RB65</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="n">
         <v>226</v>
       </c>
-      <c r="C197" s="4" t="n">
-        <v>193</v>
-      </c>
-      <c r="D197" s="3" t="inlineStr">
-        <is>
-          <t>Jaylin Noel</t>
-        </is>
-      </c>
-      <c r="E197" s="3" t="inlineStr">
-        <is>
-          <t>HOU (6)</t>
-        </is>
-      </c>
-      <c r="F197" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>WR82</t>
-        </is>
-      </c>
-      <c r="B198" s="3" t="n">
-        <v>227</v>
-      </c>
-      <c r="C198" s="4" t="n">
-        <v>209</v>
+      <c r="C198" s="10" t="n">
+        <v>189</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Calvin AustinI</t>
+          <t>Chris Rodriguez</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>PIT (5)</t>
+          <t>WAS (12)</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>RB64</t>
+          <t>RB66</t>
         </is>
       </c>
       <c r="B199" s="3" t="n">
-        <v>228</v>
-      </c>
-      <c r="C199" s="10" t="n">
-        <v>156</v>
+        <v>227</v>
+      </c>
+      <c r="C199" s="4" t="n">
+        <v>225</v>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Miles Sanders</t>
+          <t>Kareem Hunt</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>DAL (10)</t>
+          <t>KC (10)</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
@@ -6076,74 +6076,74 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>WR83</t>
+          <t>WR81</t>
         </is>
       </c>
       <c r="B200" s="3" t="n">
+        <v>228</v>
+      </c>
+      <c r="C200" s="4" t="n">
+        <v>203</v>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>Jaylin Noel (R)</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>HOU (6)</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="inlineStr">
+        <is>
+          <t>RB67</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="n">
         <v>229</v>
       </c>
-      <c r="C200" s="4" t="n">
-        <v>223</v>
-      </c>
-      <c r="D200" s="3" t="inlineStr">
-        <is>
-          <t>Tyler Lockett</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>TEN (10)</t>
-        </is>
-      </c>
-      <c r="F200" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>WR84</t>
-        </is>
-      </c>
-      <c r="B201" s="3" t="n">
-        <v>230</v>
-      </c>
-      <c r="C201" s="4" t="n">
-        <v>254</v>
+      <c r="C201" s="10" t="n">
+        <v>191</v>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Elic Ayomanor</t>
+          <t>Kendre Miller</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>TEN (10)</t>
+          <t>NO (11)</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
         <is>
-          <t>RB65</t>
+          <t>RB68</t>
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C202" s="4" t="n">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Kyle Monangai</t>
+          <t>Kyle Monangai (R)</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
@@ -6160,303 +6160,303 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
+          <t>WR82</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="C203" s="4" t="n">
+        <v>249</v>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>Jalen McMillan</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>TB (9)</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="8" t="inlineStr">
+        <is>
+          <t>TE27</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="n">
+        <v>232</v>
+      </c>
+      <c r="C204" s="10" t="n">
+        <v>175</v>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>Dalton Schultz</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>HOU (6)</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="11" t="inlineStr">
+        <is>
+          <t>QB30</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="n">
+        <v>233</v>
+      </c>
+      <c r="C205" s="4" t="n">
+        <v>207</v>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>Russell Wilson</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>NYG (14)</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="inlineStr">
+        <is>
+          <t>RB69</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="C206" s="4" t="n">
+        <v>222</v>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>GB (5)</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>WR83</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="C207" s="4" t="n">
+        <v>236</v>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Calvin AustinI</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>PIT (5)</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>WR84</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="n">
+        <v>236</v>
+      </c>
+      <c r="C208" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Tyler Lockett</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>TEN (10)</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>RB70</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="n">
+        <v>237</v>
+      </c>
+      <c r="C209" s="10" t="n">
+        <v>190</v>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>Keaton Mitchell</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>BAL (7)</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
           <t>WR85</t>
         </is>
       </c>
-      <c r="B203" s="3" t="n">
-        <v>232</v>
-      </c>
-      <c r="C203" s="4" t="n">
-        <v>219</v>
-      </c>
-      <c r="D203" s="3" t="inlineStr">
-        <is>
-          <t>Pat Bryant</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>DEN (12)</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="11" t="inlineStr">
-        <is>
-          <t>QB30</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="n">
-        <v>233</v>
-      </c>
-      <c r="C204" s="10" t="n">
-        <v>186</v>
-      </c>
-      <c r="D204" s="3" t="inlineStr">
-        <is>
-          <t>Russell Wilson</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>NYG (14)</t>
-        </is>
-      </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="5" t="inlineStr">
-        <is>
-          <t>RB66</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="n">
-        <v>234</v>
-      </c>
-      <c r="C205" s="10" t="n">
-        <v>187</v>
-      </c>
-      <c r="D205" s="3" t="inlineStr">
-        <is>
-          <t>DJ Giddens</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>IND (11)</t>
-        </is>
-      </c>
-      <c r="F205" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>WR86</t>
-        </is>
-      </c>
-      <c r="B206" s="3" t="n">
-        <v>235</v>
-      </c>
-      <c r="C206" s="4" t="n">
-        <v>248</v>
-      </c>
-      <c r="D206" s="3" t="inlineStr">
-        <is>
-          <t>Diontae Johnson</t>
-        </is>
-      </c>
-      <c r="E206" s="3" t="inlineStr">
-        <is>
-          <t>CLE (9)</t>
-        </is>
-      </c>
-      <c r="F206" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="5" t="inlineStr">
-        <is>
-          <t>RB67</t>
-        </is>
-      </c>
-      <c r="B207" s="3" t="n">
-        <v>236</v>
-      </c>
-      <c r="C207" s="4" t="n">
-        <v>230</v>
-      </c>
-      <c r="D207" s="3" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>HOU (6)</t>
-        </is>
-      </c>
-      <c r="F207" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="8" t="inlineStr">
+      <c r="B210" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="C210" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>Dontayvion Wicks</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>GB (5)</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="8" t="inlineStr">
         <is>
           <t>TE28</t>
         </is>
       </c>
-      <c r="B208" s="3" t="n">
-        <v>238</v>
-      </c>
-      <c r="C208" s="10" t="n">
-        <v>199</v>
-      </c>
-      <c r="D208" s="3" t="inlineStr">
-        <is>
-          <t>Juwan Johnson</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>NO (11)</t>
-        </is>
-      </c>
-      <c r="F208" s="3" t="inlineStr">
+      <c r="B211" s="3" t="n">
+        <v>241</v>
+      </c>
+      <c r="C211" s="4" t="n">
+        <v>208</v>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>Ja'Tavion Sanders</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>CAR (14)</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="8" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="8" t="inlineStr">
         <is>
           <t>TE29</t>
         </is>
       </c>
-      <c r="B209" s="3" t="n">
-        <v>239</v>
-      </c>
-      <c r="C209" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="D209" s="3" t="inlineStr">
-        <is>
-          <t>Ja'Tavion Sanders</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>CAR (14)</t>
-        </is>
-      </c>
-      <c r="F209" s="3" t="inlineStr">
+      <c r="B212" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="C212" s="4" t="n">
+        <v>252</v>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>Elijah Arroyo (R)</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>SEA (8)</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="8" t="inlineStr">
-        <is>
-          <t>TE30</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="n">
-        <v>241</v>
-      </c>
-      <c r="C210" s="4" t="n">
-        <v>231</v>
-      </c>
-      <c r="D210" s="3" t="inlineStr">
-        <is>
-          <t>Elijah Arroyo</t>
-        </is>
-      </c>
-      <c r="E210" s="3" t="inlineStr">
-        <is>
-          <t>SEA (8)</t>
-        </is>
-      </c>
-      <c r="F210" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="5" t="inlineStr">
-        <is>
-          <t>RB68</t>
-        </is>
-      </c>
-      <c r="B211" s="3" t="n">
-        <v>242</v>
-      </c>
-      <c r="C211" s="10" t="n">
-        <v>177</v>
-      </c>
-      <c r="D211" s="3" t="inlineStr">
-        <is>
-          <t>Keaton Mitchell</t>
-        </is>
-      </c>
-      <c r="E211" s="3" t="inlineStr">
-        <is>
-          <t>BAL (7)</t>
-        </is>
-      </c>
-      <c r="F211" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>WR87</t>
-        </is>
-      </c>
-      <c r="B212" s="3" t="n">
-        <v>243</v>
-      </c>
-      <c r="C212" s="4" t="n">
-        <v>233</v>
-      </c>
-      <c r="D212" s="3" t="inlineStr">
-        <is>
-          <t>Devaughn Vele</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="inlineStr">
-        <is>
-          <t>DEN (12)</t>
-        </is>
-      </c>
-      <c r="F212" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>RB69</t>
+          <t>RB71</t>
         </is>
       </c>
       <c r="B213" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="C213" s="4" t="n">
-        <v>261</v>
+        <v>243</v>
+      </c>
+      <c r="C213" s="10" t="n">
+        <v>157</v>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>Jaleel McLaughlin</t>
+          <t>Dameon Pierce</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>DEN (12)</t>
+          <t>HOU (6)</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -6468,14 +6468,14 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>WR88</t>
+          <t>WR86</t>
         </is>
       </c>
       <c r="B214" s="3" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C214" s="10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
@@ -6496,46 +6496,46 @@
     <row r="215">
       <c r="A215" s="8" t="inlineStr">
         <is>
-          <t>TE31</t>
+          <t>TE30</t>
         </is>
       </c>
       <c r="B215" s="3" t="n">
+        <v>245</v>
+      </c>
+      <c r="C215" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>Juwan Johnson</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>NO (11)</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>RB72</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="n">
         <v>246</v>
       </c>
-      <c r="C215" s="4" t="n">
-        <v>239</v>
-      </c>
-      <c r="D215" s="3" t="inlineStr">
-        <is>
-          <t>Cole Kmet</t>
-        </is>
-      </c>
-      <c r="E215" s="3" t="inlineStr">
-        <is>
-          <t>CHI (5)</t>
-        </is>
-      </c>
-      <c r="F215" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>WR90</t>
-        </is>
-      </c>
-      <c r="B216" s="3" t="n">
-        <v>249</v>
-      </c>
       <c r="C216" s="4" t="n">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Jalen Royals</t>
+          <t>Brashard Smith (R)</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
@@ -6545,25 +6545,25 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>RB70</t>
+          <t>RB73</t>
         </is>
       </c>
       <c r="B217" s="3" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C217" s="10" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>Tahj Brooks</t>
+          <t>Tahj Brooks (R)</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
@@ -6580,23 +6580,23 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>WR91</t>
+          <t>WR87</t>
         </is>
       </c>
       <c r="B218" s="3" t="n">
-        <v>252</v>
-      </c>
-      <c r="C218" s="4" t="n">
-        <v>265</v>
+        <v>248</v>
+      </c>
+      <c r="C218" s="10" t="n">
+        <v>199</v>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Brandin Cooks</t>
+          <t>Dont'e Thornton (R)</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>NO (11)</t>
+          <t>LV (8)</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
@@ -6608,23 +6608,23 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>WR92</t>
+          <t>WR88</t>
         </is>
       </c>
       <c r="B219" s="3" t="n">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Jalen Royals (R)</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>DAL (10)</t>
+          <t>KC (10)</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
@@ -6634,53 +6634,53 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="5" t="inlineStr">
-        <is>
-          <t>RB71</t>
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>WR89</t>
         </is>
       </c>
       <c r="B220" s="3" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Jarquez Hunter</t>
+          <t>Tory Horton (R)</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>LAR (8)</t>
+          <t>SEA (8)</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>RB72</t>
+          <t>RB74</t>
         </is>
       </c>
       <c r="B221" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="C221" s="4" t="n">
-        <v>245</v>
+        <v>252</v>
+      </c>
+      <c r="C221" s="10" t="n">
+        <v>195</v>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>Brashard Smith</t>
+          <t>Miles Sanders</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>KC (10)</t>
+          <t>DAL (10)</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -6690,20 +6690,20 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="5" t="inlineStr">
-        <is>
-          <t>RB73</t>
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>WR90</t>
         </is>
       </c>
       <c r="B222" s="3" t="n">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C222" s="4" t="n">
-        <v>268</v>
+        <v>234</v>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Devin Neal</t>
+          <t>Devaughn Vele</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
@@ -6713,35 +6713,35 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="5" t="inlineStr">
-        <is>
-          <t>RB74</t>
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>WR91</t>
         </is>
       </c>
       <c r="B223" s="3" t="n">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C223" s="4" t="n">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>Raheem Mostert</t>
+          <t>Roman Wilson</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>LV (8)</t>
+          <t>PIT (5)</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
@@ -6752,187 +6752,187 @@
         </is>
       </c>
       <c r="B224" s="3" t="n">
+        <v>256</v>
+      </c>
+      <c r="C224" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>Jaleel McLaughlin</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>DEN (12)</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="8" t="inlineStr">
+        <is>
+          <t>TE31</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="C225" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>Cole Kmet</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>CHI (5)</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="inlineStr">
+        <is>
+          <t>RB76</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="C226" s="4" t="n">
+        <v>221</v>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>Jarquez Hunter (R)</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>LAR (8)</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="11" t="inlineStr">
+        <is>
+          <t>QB31</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="C224" s="4" t="n">
-        <v>259</v>
-      </c>
-      <c r="D224" s="3" t="inlineStr">
-        <is>
-          <t>Ollie Gordon</t>
-        </is>
-      </c>
-      <c r="E224" s="3" t="inlineStr">
-        <is>
-          <t>MIA (12)</t>
-        </is>
-      </c>
-      <c r="F224" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="5" t="inlineStr">
-        <is>
-          <t>RB76</t>
-        </is>
-      </c>
-      <c r="B225" s="3" t="n">
+      <c r="C227" s="4" t="n">
+        <v>214</v>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>Anthony Richardson</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>IND (11)</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="11" t="inlineStr">
+        <is>
+          <t>QB32</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="n">
+        <v>261</v>
+      </c>
+      <c r="C228" s="4" t="n">
+        <v>213</v>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>Joe Flacco</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>CLE (9)</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>WR92</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="n">
         <v>262</v>
       </c>
-      <c r="C225" s="10" t="n">
-        <v>189</v>
-      </c>
-      <c r="D225" s="3" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
-      <c r="E225" s="3" t="inlineStr">
-        <is>
-          <t>WAS (12)</t>
-        </is>
-      </c>
-      <c r="F225" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>WR95</t>
-        </is>
-      </c>
-      <c r="B226" s="3" t="n">
-        <v>264</v>
-      </c>
-      <c r="C226" s="4" t="n">
-        <v>251</v>
-      </c>
-      <c r="D226" s="3" t="inlineStr">
-        <is>
-          <t>Nick Westbrook-Ikhine</t>
-        </is>
-      </c>
-      <c r="E226" s="3" t="inlineStr">
-        <is>
-          <t>MIA (12)</t>
-        </is>
-      </c>
-      <c r="F226" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="5" t="inlineStr">
-        <is>
-          <t>RB77</t>
-        </is>
-      </c>
-      <c r="B227" s="3" t="n">
-        <v>265</v>
-      </c>
-      <c r="C227" s="4" t="n">
-        <v>260</v>
-      </c>
-      <c r="D227" s="3" t="inlineStr">
-        <is>
-          <t>Elijah Mitchell</t>
-        </is>
-      </c>
-      <c r="E227" s="3" t="inlineStr">
-        <is>
-          <t>KC (10)</t>
-        </is>
-      </c>
-      <c r="F227" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>WR96</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="n">
-        <v>266</v>
-      </c>
-      <c r="C228" s="4" t="n">
-        <v>225</v>
-      </c>
-      <c r="D228" s="3" t="inlineStr">
-        <is>
-          <t>Dont'e Thornton</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="inlineStr">
-        <is>
-          <t>LV (8)</t>
-        </is>
-      </c>
-      <c r="F228" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="11" t="inlineStr">
-        <is>
-          <t>QB31</t>
-        </is>
-      </c>
-      <c r="B229" s="3" t="n">
-        <v>268</v>
-      </c>
-      <c r="C229" s="10" t="n">
-        <v>185</v>
+      <c r="C229" s="4" t="n">
+        <v>215</v>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>Daniel Jones</t>
+          <t>Isaac TeSlaa (R)</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>IND (11)</t>
+          <t>DET (8)</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>WR98</t>
+          <t>WR93</t>
         </is>
       </c>
       <c r="B230" s="3" t="n">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C230" s="4" t="n">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>Tory Horton</t>
+          <t>Malik Washington</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>SEA (8)</t>
+          <t>MIA (12)</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -6944,23 +6944,23 @@
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>RB80</t>
+          <t>RB77</t>
         </is>
       </c>
       <c r="B231" s="3" t="n">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="C231" s="4" t="n">
-        <v>213</v>
+        <v>276</v>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>Sean Tucker</t>
+          <t>Devin Neal (R)</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>TB (9)</t>
+          <t>NO (11)</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
@@ -6970,165 +6970,165 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="5" t="inlineStr">
-        <is>
-          <t>RB81</t>
+      <c r="A232" s="8" t="inlineStr">
+        <is>
+          <t>TE32</t>
         </is>
       </c>
       <c r="B232" s="3" t="n">
-        <v>273</v>
-      </c>
-      <c r="C232" s="4" t="n">
-        <v>244</v>
+        <v>265</v>
+      </c>
+      <c r="C232" s="10" t="n">
+        <v>194</v>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>Trevor Etienne</t>
+          <t>Harold Fannin (R)</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>CAR (14)</t>
+          <t>CLE (9)</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="8" t="inlineStr">
-        <is>
-          <t>TE32</t>
+      <c r="A233" s="5" t="inlineStr">
+        <is>
+          <t>RB78</t>
         </is>
       </c>
       <c r="B233" s="3" t="n">
-        <v>275</v>
-      </c>
-      <c r="C233" s="10" t="n">
-        <v>172</v>
+        <v>266</v>
+      </c>
+      <c r="C233" s="4" t="n">
+        <v>224</v>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
+          <t>Raheem Mostert</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>LV (8)</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>WR94</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="C234" s="4" t="n">
+        <v>264</v>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>Brandin Cooks</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>NO (11)</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>WR95</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="C235" s="4" t="n">
+        <v>261</v>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Jalen Tolbert</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>DAL (10)</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="8" t="inlineStr">
+        <is>
+          <t>TE33</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="C236" s="10" t="n">
+        <v>168</v>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
           <t>Theo Johnson</t>
         </is>
       </c>
-      <c r="E233" s="3" t="inlineStr">
+      <c r="E236" s="3" t="inlineStr">
         <is>
           <t>NYG (14)</t>
         </is>
       </c>
-      <c r="F233" s="3" t="inlineStr">
+      <c r="F236" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="11" t="inlineStr">
-        <is>
-          <t>QB32</t>
-        </is>
-      </c>
-      <c r="B234" s="3" t="n">
-        <v>276</v>
-      </c>
-      <c r="C234" s="4" t="n">
-        <v>262</v>
-      </c>
-      <c r="D234" s="3" t="inlineStr">
-        <is>
-          <t>Joe Flacco</t>
-        </is>
-      </c>
-      <c r="E234" s="3" t="inlineStr">
-        <is>
-          <t>CLE (9)</t>
-        </is>
-      </c>
-      <c r="F234" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="8" t="inlineStr">
-        <is>
-          <t>TE33</t>
-        </is>
-      </c>
-      <c r="B235" s="3" t="n">
-        <v>278</v>
-      </c>
-      <c r="C235" s="4" t="n">
-        <v>250</v>
-      </c>
-      <c r="D235" s="3" t="inlineStr">
-        <is>
-          <t>Noah Gray</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="inlineStr">
-        <is>
-          <t>KC (10)</t>
-        </is>
-      </c>
-      <c r="F235" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>WR99</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="n">
-        <v>279</v>
-      </c>
-      <c r="C236" s="4" t="n">
-        <v>210</v>
-      </c>
-      <c r="D236" s="3" t="inlineStr">
-        <is>
-          <t>Tre Tucker</t>
-        </is>
-      </c>
-      <c r="E236" s="3" t="inlineStr">
-        <is>
-          <t>LV (8)</t>
-        </is>
-      </c>
-      <c r="F236" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>RB84</t>
+          <t>RB79</t>
         </is>
       </c>
       <c r="B237" s="3" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>Devin Singletary</t>
+          <t>Sean Tucker</t>
         </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>NYG (14)</t>
+          <t>TB (9)</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
@@ -7138,109 +7138,109 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="8" t="inlineStr">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>WR97</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="n">
+        <v>273</v>
+      </c>
+      <c r="C238" s="4" t="n">
+        <v>243</v>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>Kayshon Boutte</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>NE (14)</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>RB81</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="C239" s="4" t="n">
+        <v>246</v>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Trevor Etienne (R)</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>CAR (14)</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="8" t="inlineStr">
         <is>
           <t>TE34</t>
         </is>
       </c>
-      <c r="B238" s="3" t="n">
-        <v>281</v>
-      </c>
-      <c r="C238" s="4" t="n">
-        <v>256</v>
-      </c>
-      <c r="D238" s="3" t="inlineStr">
-        <is>
-          <t>Harold Fannin</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="inlineStr">
-        <is>
-          <t>CLE (9)</t>
-        </is>
-      </c>
-      <c r="F238" s="3" t="inlineStr">
+      <c r="B240" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="C240" s="4" t="n">
+        <v>242</v>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Noah Gray</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>KC (10)</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="11" t="inlineStr">
-        <is>
-          <t>QB33</t>
-        </is>
-      </c>
-      <c r="B239" s="3" t="n">
-        <v>283</v>
-      </c>
-      <c r="C239" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="D239" s="3" t="inlineStr">
-        <is>
-          <t>Tyler Shough</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="inlineStr">
-        <is>
-          <t>NO (11)</t>
-        </is>
-      </c>
-      <c r="F239" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="5" t="inlineStr">
-        <is>
-          <t>RB85</t>
-        </is>
-      </c>
-      <c r="B240" s="3" t="n">
-        <v>285</v>
-      </c>
-      <c r="C240" s="4" t="n">
-        <v>215</v>
-      </c>
-      <c r="D240" s="3" t="inlineStr">
-        <is>
-          <t>Isaiah Davis</t>
-        </is>
-      </c>
-      <c r="E240" s="3" t="inlineStr">
-        <is>
-          <t>NYJ (9)</t>
-        </is>
-      </c>
-      <c r="F240" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>WR101</t>
+          <t>WR98</t>
         </is>
       </c>
       <c r="B241" s="3" t="n">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="C241" s="4" t="n">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>Isaac TeSlaa</t>
+          <t>Nick Westbrook-Ikhine</t>
         </is>
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>DET (8)</t>
+          <t>MIA (12)</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -7250,165 +7250,165 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>WR103</t>
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>RB83</t>
         </is>
       </c>
       <c r="B242" s="3" t="n">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="C242" s="4" t="n">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>Amari Cooper</t>
+          <t>Elijah Mitchell</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>FA (-)</t>
+          <t>KC (10)</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="8" t="inlineStr">
-        <is>
-          <t>TE35</t>
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>WR99</t>
         </is>
       </c>
       <c r="B243" s="3" t="n">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="C243" s="4" t="n">
-        <v>207</v>
+        <v>279</v>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>Darren Waller</t>
+          <t>Amari Cooper (?)</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>MIA (12)</t>
+          <t>LV (8)</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="inlineStr">
-        <is>
-          <t>RB87</t>
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>WR100</t>
         </is>
       </c>
       <c r="B244" s="3" t="n">
-        <v>292</v>
-      </c>
-      <c r="C244" s="4" t="n">
-        <v>229</v>
+        <v>283</v>
+      </c>
+      <c r="C244" s="10" t="n">
+        <v>198</v>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>Dameon Pierce</t>
+          <t>Tre Tucker</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>HOU (6)</t>
+          <t>LV (8)</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="11" t="inlineStr">
         <is>
+          <t>QB33</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="C245" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>Jaxson Dart (R)</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>NYG (14)</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="11" t="inlineStr">
+        <is>
           <t>QB34</t>
         </is>
       </c>
-      <c r="B245" s="3" t="n">
-        <v>294</v>
-      </c>
-      <c r="C245" s="10" t="n">
-        <v>178</v>
-      </c>
-      <c r="D245" s="3" t="inlineStr">
-        <is>
-          <t>Jaxson Dart</t>
-        </is>
-      </c>
-      <c r="E245" s="3" t="inlineStr">
-        <is>
-          <t>NYG (14)</t>
-        </is>
-      </c>
-      <c r="F245" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="8" t="inlineStr">
-        <is>
-          <t>TE37</t>
-        </is>
-      </c>
       <c r="B246" s="3" t="n">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="C246" s="4" t="n">
         <v>232</v>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Terrance Ferguson</t>
+          <t>Tyler Shough (R)</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>LAR (8)</t>
+          <t>NO (11)</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="8" t="inlineStr">
         <is>
-          <t>TE38</t>
+          <t>TE35</t>
         </is>
       </c>
       <c r="B247" s="3" t="n">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>Noah Fant</t>
+          <t>Darren Waller</t>
         </is>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>CIN (10)</t>
+          <t>MIA (12)</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
@@ -7420,23 +7420,23 @@
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
         <is>
-          <t>RB92</t>
+          <t>RB85</t>
         </is>
       </c>
       <c r="B248" s="3" t="n">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="C248" s="4" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>Phil Mafah</t>
+          <t>Devin Singletary</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>DAL (10)</t>
+          <t>NYG (14)</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
@@ -7446,81 +7446,81 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="8" t="inlineStr">
-        <is>
-          <t>TE39</t>
+      <c r="A249" s="11" t="inlineStr">
+        <is>
+          <t>QB35</t>
         </is>
       </c>
       <c r="B249" s="3" t="n">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="C249" s="4" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>Tyler Higbee</t>
+          <t>Spencer Rattler</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>LAR (8)</t>
+          <t>NO (11)</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="8" t="inlineStr">
-        <is>
-          <t>TE40</t>
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>WR101</t>
         </is>
       </c>
       <c r="B250" s="3" t="n">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="C250" s="4" t="n">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>Oronde Gadsden</t>
+          <t>Diontae Johnson</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>LAC (12)</t>
+          <t>FA (-)</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>WR110</t>
+          <t>WR102</t>
         </is>
       </c>
       <c r="B251" s="3" t="n">
-        <v>319</v>
+        <v>290</v>
       </c>
       <c r="C251" s="4" t="n">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>Tutu Atwell</t>
+          <t>Jalen Nailor</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>LAR (8)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
@@ -7530,53 +7530,53 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>WR112</t>
+      <c r="A252" s="5" t="inlineStr">
+        <is>
+          <t>RB86</t>
         </is>
       </c>
       <c r="B252" s="3" t="n">
-        <v>322</v>
+        <v>291</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>Ray-Ray McCloudI</t>
+          <t>Isaiah Davis</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>ATL (5)</t>
+          <t>NYJ (9)</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="8" t="inlineStr">
         <is>
-          <t>TE41</t>
+          <t>TE37</t>
         </is>
       </c>
       <c r="B253" s="3" t="n">
-        <v>326</v>
+        <v>302</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>Will Dissly</t>
+          <t>Terrance Ferguson (R)</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>LAC (12)</t>
+          <t>LAR (8)</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
@@ -7588,23 +7588,23 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>WR113</t>
+          <t>WR106</t>
         </is>
       </c>
       <c r="B254" s="3" t="n">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="C254" s="4" t="n">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>Josh Reynolds</t>
+          <t>Troy Franklin</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>NYJ (9)</t>
+          <t>DEN (12)</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
@@ -7614,53 +7614,53 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="8" t="inlineStr">
-        <is>
-          <t>TE42</t>
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>WR107</t>
         </is>
       </c>
       <c r="B255" s="3" t="n">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="C255" s="4" t="n">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>Ben Sinnott</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>WAS (12)</t>
+          <t>GB (5)</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>WR117</t>
+          <t>WR108</t>
         </is>
       </c>
       <c r="B256" s="3" t="n">
-        <v>336</v>
+        <v>307</v>
       </c>
       <c r="C256" s="4" t="n">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>KaVontae Turpin</t>
+          <t>Ray-Ray McCloudI</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>DAL (10)</t>
+          <t>ATL (5)</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
@@ -7670,53 +7670,53 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="11" t="inlineStr">
-        <is>
-          <t>QB36</t>
+      <c r="A257" s="8" t="inlineStr">
+        <is>
+          <t>TE38</t>
         </is>
       </c>
       <c r="B257" s="3" t="n">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>Spencer Rattler</t>
+          <t>Noah Fant</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>NO (11)</t>
+          <t>CIN (10)</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>WR118</t>
+          <t>WR110</t>
         </is>
       </c>
       <c r="B258" s="3" t="n">
-        <v>339</v>
+        <v>311</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>Tai Felton</t>
+          <t>Tutu Atwell</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>LAR (8)</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
@@ -7726,198 +7726,534 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="11" t="inlineStr">
-        <is>
-          <t>QB37</t>
+      <c r="A259" s="8" t="inlineStr">
+        <is>
+          <t>TE39</t>
         </is>
       </c>
       <c r="B259" s="3" t="n">
-        <v>342</v>
+        <v>314</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>Jalen Milroe</t>
+          <t>Tyler Higbee</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>SEA (8)</t>
+          <t>LAR (8)</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>WR120</t>
+      <c r="A260" s="5" t="inlineStr">
+        <is>
+          <t>RB95</t>
         </is>
       </c>
       <c r="B260" s="3" t="n">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="C260" s="4" t="n">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>Marquez Valdes-Scantling</t>
+          <t>Phil Mafah (R)</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>SEA (8)</t>
+          <t>DAL (10)</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="inlineStr">
-        <is>
-          <t>WR124</t>
+      <c r="A261" s="8" t="inlineStr">
+        <is>
+          <t>TE40</t>
         </is>
       </c>
       <c r="B261" s="3" t="n">
-        <v>355</v>
+        <v>322</v>
       </c>
       <c r="C261" s="4" t="n">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>Chimere Dike</t>
+          <t>Oronde Gadsden (R)</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>TEN (10)</t>
+          <t>LAC (12)</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="11" t="inlineStr">
-        <is>
-          <t>QB38</t>
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>WR114</t>
         </is>
       </c>
       <c r="B262" s="3" t="n">
-        <v>358</v>
+        <v>326</v>
       </c>
       <c r="C262" s="4" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>Kirk Cousins</t>
+          <t>Josh Reynolds</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>ATL (5)</t>
+          <t>NYJ (9)</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>WR128</t>
+      <c r="A263" s="8" t="inlineStr">
+        <is>
+          <t>TE41</t>
         </is>
       </c>
       <c r="B263" s="3" t="n">
-        <v>366</v>
+        <v>329</v>
       </c>
       <c r="C263" s="4" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>Allen Lazard</t>
+          <t>Ben Sinnott</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>NYJ (9)</t>
+          <t>WAS (12)</t>
         </is>
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="11" t="inlineStr">
-        <is>
-          <t>QB41</t>
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>WR115</t>
         </is>
       </c>
       <c r="B264" s="3" t="n">
-        <v>378</v>
+        <v>330</v>
       </c>
       <c r="C264" s="4" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>Kenny Pickett</t>
+          <t>Noah Brown</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>CLE (9)</t>
+          <t>WAS (12)</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>WR136</t>
+          <t>WR116</t>
         </is>
       </c>
       <c r="B265" s="3" t="n">
-        <v>381</v>
+        <v>331</v>
       </c>
       <c r="C265" s="4" t="n">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
+          <t>KaVontae Turpin</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>DAL (10)</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="8" t="inlineStr">
+        <is>
+          <t>TE43</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="n">
+        <v>333</v>
+      </c>
+      <c r="C266" s="4" t="n">
+        <v>273</v>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>Will Dissly</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>LAC (12)</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="11" t="inlineStr">
+        <is>
+          <t>QB37</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="n">
+        <v>338</v>
+      </c>
+      <c r="C267" s="4" t="n">
+        <v>259</v>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>Jalen Milroe (R)</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>SEA (8)</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>WR118</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="n">
+        <v>340</v>
+      </c>
+      <c r="C268" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>KeAndre Lambert-Smith (R)</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>LAC (12)</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>WR123</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="n">
+        <v>349</v>
+      </c>
+      <c r="C269" s="4" t="n">
+        <v>268</v>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>Tai Felton (R)</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>MIN (6)</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>WR124</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="n">
+        <v>351</v>
+      </c>
+      <c r="C270" s="4" t="n">
+        <v>239</v>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>Olamide Zaccheaus</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>CHI (5)</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="8" t="inlineStr">
+        <is>
+          <t>TE46</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="n">
+        <v>352</v>
+      </c>
+      <c r="C271" s="4" t="n">
+        <v>212</v>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>AJ Barner</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>SEA (8)</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="11" t="inlineStr">
+        <is>
+          <t>QB38</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="n">
+        <v>354</v>
+      </c>
+      <c r="C272" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>Kirk Cousins (?)</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>ATL (5)</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>WR125</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="n">
+        <v>355</v>
+      </c>
+      <c r="C273" s="4" t="n">
+        <v>262</v>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>Marquez Valdes-Scantling</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>SF (14)</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>WR126</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="n">
+        <v>357</v>
+      </c>
+      <c r="C274" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>Allen Lazard</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>NYJ (9)</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>WR128</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="n">
+        <v>361</v>
+      </c>
+      <c r="C275" s="4" t="n">
+        <v>277</v>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>Chimere Dike (R)</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>TEN (10)</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>WR132</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="n">
+        <v>374</v>
+      </c>
+      <c r="C276" s="4" t="n">
+        <v>266</v>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
           <t>Jahan Dotson</t>
         </is>
       </c>
-      <c r="E265" s="3" t="inlineStr">
+      <c r="E276" s="3" t="inlineStr">
         <is>
           <t>PHI (9)</t>
         </is>
       </c>
-      <c r="F265" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="11" t="inlineStr">
+        <is>
+          <t>QB42</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="n">
+        <v>393</v>
+      </c>
+      <c r="C277" s="4" t="n">
+        <v>257</v>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>Kenny Pickett</t>
+        </is>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
+        <is>
+          <t>LV (8)</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
     </row>
